--- a/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_7.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_7.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -227,6 +227,63 @@
   </si>
   <si>
     <t>TK_DAY</t>
+  </si>
+  <si>
+    <t>TAIL_NUMBER</t>
+  </si>
+  <si>
+    <t>INIT_AIRPORT</t>
+  </si>
+  <si>
+    <t>INIT_FLYING_TIME</t>
+  </si>
+  <si>
+    <t>INIT_TAKEOFF</t>
+  </si>
+  <si>
+    <t>INIT_FLYING_DAY</t>
+  </si>
+  <si>
+    <t>N121</t>
+  </si>
+  <si>
+    <t>SAW</t>
+  </si>
+  <si>
+    <t>N122</t>
+  </si>
+  <si>
+    <t>ESB</t>
+  </si>
+  <si>
+    <t>N123</t>
+  </si>
+  <si>
+    <t>N124</t>
+  </si>
+  <si>
+    <t>HTY</t>
+  </si>
+  <si>
+    <t>N125</t>
+  </si>
+  <si>
+    <t>ECN</t>
+  </si>
+  <si>
+    <t>N126</t>
+  </si>
+  <si>
+    <t>YEI</t>
+  </si>
+  <si>
+    <t>N127</t>
+  </si>
+  <si>
+    <t>N128</t>
+  </si>
+  <si>
+    <t>MLX</t>
   </si>
 </sst>
 </file>
@@ -516,7 +573,7 @@
   <dimension ref="A1:H355"/>
   <sheetFormatPr defaultColWidth="10.62109375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
@@ -542,7 +599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2" t="n" s="1">
         <v>2011</v>
       </c>
@@ -568,7 +625,7 @@
         <v>31980</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="3" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A3" t="n" s="1">
         <v>2011</v>
       </c>
@@ -594,7 +651,7 @@
         <v>31990</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="4" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A4" t="n" s="1">
         <v>2011</v>
       </c>
@@ -620,7 +677,7 @@
         <v>31980</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="5" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A5" t="n" s="1">
         <v>2011</v>
       </c>
@@ -646,7 +703,7 @@
         <v>31995</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="6" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A6" t="n" s="1">
         <v>2011</v>
       </c>
@@ -672,7 +729,7 @@
         <v>31995</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="7" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A7" t="n" s="1">
         <v>2011</v>
       </c>
@@ -698,7 +755,7 @@
         <v>32040</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="8" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A8" t="n" s="1">
         <v>2011</v>
       </c>
@@ -724,7 +781,7 @@
         <v>32075</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="9" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A9" t="n" s="1">
         <v>2011</v>
       </c>
@@ -750,7 +807,7 @@
         <v>32100</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="10" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A10" t="n" s="1">
         <v>2011</v>
       </c>
@@ -776,7 +833,7 @@
         <v>32120</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="11" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A11" t="n" s="1">
         <v>2011</v>
       </c>
@@ -802,7 +859,7 @@
         <v>32145</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="12" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A12" t="n" s="1">
         <v>2011</v>
       </c>
@@ -828,7 +885,7 @@
         <v>32155</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="13" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A13" t="n" s="1">
         <v>2011</v>
       </c>
@@ -854,7 +911,7 @@
         <v>32220</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="14" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A14" t="n" s="1">
         <v>2011</v>
       </c>
@@ -880,7 +937,7 @@
         <v>32245</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="15" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A15" t="n" s="1">
         <v>2011</v>
       </c>
@@ -906,7 +963,7 @@
         <v>32235</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="16" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A16" t="n" s="1">
         <v>2011</v>
       </c>
@@ -932,7 +989,7 @@
         <v>32220</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="17" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A17" t="n" s="1">
         <v>2011</v>
       </c>
@@ -958,7 +1015,7 @@
         <v>32285</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="18" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A18" t="n" s="1">
         <v>2011</v>
       </c>
@@ -984,7 +1041,7 @@
         <v>32285</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="19" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A19" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1010,7 +1067,7 @@
         <v>32360</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="20" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A20" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1036,7 +1093,7 @@
         <v>32385</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="21" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A21" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1062,7 +1119,7 @@
         <v>32340</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="22" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A22" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1088,7 +1145,7 @@
         <v>32425</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="23" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A23" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1114,7 +1171,7 @@
         <v>32410</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="24" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A24" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1140,7 +1197,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="25" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A25" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1166,7 +1223,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="26" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A26" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1192,7 +1249,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="27" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A27" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1218,7 +1275,7 @@
         <v>32460</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="28" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A28" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1244,7 +1301,7 @@
         <v>32555</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="29" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A29" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1270,7 +1327,7 @@
         <v>32565</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="30" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A30" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1296,7 +1353,7 @@
         <v>32565</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="31" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A31" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1322,7 +1379,7 @@
         <v>32570</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="32" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A32" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1348,7 +1405,7 @@
         <v>32555</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="33" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A33" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1374,7 +1431,7 @@
         <v>32580</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="34" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A34" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1400,7 +1457,7 @@
         <v>32585</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="35" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A35" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1426,7 +1483,7 @@
         <v>32680</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="36" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A36" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1452,7 +1509,7 @@
         <v>32670</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="37" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A37" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1478,7 +1535,7 @@
         <v>32695</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="38" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A38" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1504,7 +1561,7 @@
         <v>32690</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="39" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A39" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1530,7 +1587,7 @@
         <v>32700</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="40" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A40" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1556,7 +1613,7 @@
         <v>32740</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="41" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A41" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1582,7 +1639,7 @@
         <v>32720</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="42" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A42" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1608,7 +1665,7 @@
         <v>32740</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="43" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A43" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1634,7 +1691,7 @@
         <v>32765</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="44" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A44" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1660,7 +1717,7 @@
         <v>32810</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="45" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A45" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1686,7 +1743,7 @@
         <v>32805</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="46" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A46" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1712,7 +1769,7 @@
         <v>32805</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="47" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A47" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1738,7 +1795,7 @@
         <v>32815</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="48" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A48" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1764,7 +1821,7 @@
         <v>32845</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="49" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A49" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1790,7 +1847,7 @@
         <v>32865</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="50" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A50" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1816,7 +1873,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="51" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A51" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1842,7 +1899,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="52" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A52" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1868,7 +1925,7 @@
         <v>32950</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="53" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A53" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1894,7 +1951,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="54" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A54" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1920,7 +1977,7 @@
         <v>33420</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="55" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A55" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1946,7 +2003,7 @@
         <v>33430</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="56" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A56" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1972,7 +2029,7 @@
         <v>33420</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="57" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A57" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1998,7 +2055,7 @@
         <v>33435</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="58" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A58" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2024,7 +2081,7 @@
         <v>33435</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="59" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A59" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2050,7 +2107,7 @@
         <v>33480</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="60" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A60" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2076,7 +2133,7 @@
         <v>33515</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="61" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A61" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2102,7 +2159,7 @@
         <v>33540</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="62" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A62" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2128,7 +2185,7 @@
         <v>33560</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="63" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A63" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2154,7 +2211,7 @@
         <v>33585</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="64" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A64" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2180,7 +2237,7 @@
         <v>33595</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="65" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A65" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2206,7 +2263,7 @@
         <v>33660</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="66" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A66" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2232,7 +2289,7 @@
         <v>33685</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="67" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A67" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2258,7 +2315,7 @@
         <v>33675</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="68" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A68" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2284,7 +2341,7 @@
         <v>33660</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="69" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A69" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2310,7 +2367,7 @@
         <v>33725</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="70" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A70" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2336,7 +2393,7 @@
         <v>33725</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="71" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A71" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2362,7 +2419,7 @@
         <v>33800</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="72" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A72" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2388,7 +2445,7 @@
         <v>33825</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="73" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A73" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2414,7 +2471,7 @@
         <v>33780</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="74" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A74" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2440,7 +2497,7 @@
         <v>33865</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="75" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A75" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2466,7 +2523,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="76" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A76" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2492,7 +2549,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="77" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A77" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2518,7 +2575,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="78" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A78" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2544,7 +2601,7 @@
         <v>33900</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="79" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A79" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2570,7 +2627,7 @@
         <v>33995</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="80" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A80" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2596,7 +2653,7 @@
         <v>34005</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="81" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A81" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2622,7 +2679,7 @@
         <v>34005</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="82" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A82" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2648,7 +2705,7 @@
         <v>34010</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="83" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A83" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2674,7 +2731,7 @@
         <v>33995</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="84" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A84" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2700,7 +2757,7 @@
         <v>34020</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="85" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A85" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2726,7 +2783,7 @@
         <v>34120</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="86" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A86" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2752,7 +2809,7 @@
         <v>34110</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="87" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A87" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2778,7 +2835,7 @@
         <v>34135</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="88" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A88" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2804,7 +2861,7 @@
         <v>34140</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="89" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A89" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2830,7 +2887,7 @@
         <v>34180</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="90" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A90" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2856,7 +2913,7 @@
         <v>34160</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="91" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A91" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2882,7 +2939,7 @@
         <v>34205</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="92" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A92" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2908,7 +2965,7 @@
         <v>34250</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="93" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A93" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2934,7 +2991,7 @@
         <v>34245</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="94" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A94" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2960,7 +3017,7 @@
         <v>34255</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="95" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A95" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2986,7 +3043,7 @@
         <v>34305</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="96" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A96" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3012,7 +3069,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="97" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A97" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3038,7 +3095,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="98" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A98" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3064,7 +3121,7 @@
         <v>34390</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="99" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A99" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3090,7 +3147,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="100" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A100" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3116,7 +3173,7 @@
         <v>34860</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="101" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A101" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3142,7 +3199,7 @@
         <v>34870</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="102" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A102" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3168,7 +3225,7 @@
         <v>34860</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="103" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A103" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3194,7 +3251,7 @@
         <v>34875</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="104" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A104" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3220,7 +3277,7 @@
         <v>34875</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="105" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A105" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3246,7 +3303,7 @@
         <v>34920</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="106" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A106" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3272,7 +3329,7 @@
         <v>34955</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="107" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A107" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3298,7 +3355,7 @@
         <v>34980</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="108" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A108" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3324,7 +3381,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="109" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A109" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3350,7 +3407,7 @@
         <v>35025</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="110" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A110" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3376,7 +3433,7 @@
         <v>35035</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="111" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A111" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3402,7 +3459,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="112" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A112" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3428,7 +3485,7 @@
         <v>35125</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="113" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A113" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3454,7 +3511,7 @@
         <v>35170</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="114" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A114" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3480,7 +3537,7 @@
         <v>35115</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="115" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A115" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3506,7 +3563,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="116" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A116" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3532,7 +3589,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="117" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A117" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3558,7 +3615,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="118" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A118" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3584,7 +3641,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="119" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A119" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3610,7 +3667,7 @@
         <v>35240</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="120" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A120" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3636,7 +3693,7 @@
         <v>35220</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="121" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A121" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3662,7 +3719,7 @@
         <v>35265</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="122" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A122" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3688,7 +3745,7 @@
         <v>35265</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="123" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A123" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3714,7 +3771,7 @@
         <v>35305</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="124" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A124" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3740,7 +3797,7 @@
         <v>35290</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="125" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A125" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3766,7 +3823,7 @@
         <v>35390</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="126" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A126" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3792,7 +3849,7 @@
         <v>35330</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="127" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A127" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3818,7 +3875,7 @@
         <v>35330</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="128" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A128" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3844,7 +3901,7 @@
         <v>35340</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="129" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A129" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3870,7 +3927,7 @@
         <v>35435</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="130" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A130" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3896,7 +3953,7 @@
         <v>35445</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="131" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A131" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3922,7 +3979,7 @@
         <v>35450</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="132" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A132" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3948,7 +4005,7 @@
         <v>35435</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="133" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A133" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3974,7 +4031,7 @@
         <v>35460</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="134" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A134" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4000,7 +4057,7 @@
         <v>35465</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="135" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A135" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4026,7 +4083,7 @@
         <v>35560</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="136" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A136" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4052,7 +4109,7 @@
         <v>35550</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="137" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A137" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4078,7 +4135,7 @@
         <v>35575</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="138" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A138" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4104,7 +4161,7 @@
         <v>35570</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="139" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A139" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4130,7 +4187,7 @@
         <v>35580</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="140" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A140" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4156,7 +4213,7 @@
         <v>35620</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="141" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A141" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4182,7 +4239,7 @@
         <v>35600</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="142" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A142" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4208,7 +4265,7 @@
         <v>35620</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="143" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A143" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4234,7 +4291,7 @@
         <v>35645</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="144" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A144" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4260,7 +4317,7 @@
         <v>35690</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="145" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A145" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4286,7 +4343,7 @@
         <v>35685</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="146" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A146" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4312,7 +4369,7 @@
         <v>35685</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="147" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A147" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4338,7 +4395,7 @@
         <v>35695</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="148" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A148" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4364,7 +4421,7 @@
         <v>35745</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="149" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A149" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4390,7 +4447,7 @@
         <v>35725</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="150" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A150" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4416,7 +4473,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="151" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A151" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4442,7 +4499,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="152" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A152" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4468,7 +4525,7 @@
         <v>35830</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="153" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A153" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4494,7 +4551,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="154" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A154" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4520,7 +4577,7 @@
         <v>36300</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="155" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A155" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4546,7 +4603,7 @@
         <v>36310</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="156" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A156" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4572,7 +4629,7 @@
         <v>36300</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="157" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A157" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4598,7 +4655,7 @@
         <v>36315</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="158" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A158" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4624,7 +4681,7 @@
         <v>36315</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="159" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A159" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4650,7 +4707,7 @@
         <v>36360</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="160" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A160" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4676,7 +4733,7 @@
         <v>36395</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="161" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A161" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4702,7 +4759,7 @@
         <v>36420</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="162" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A162" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4728,7 +4785,7 @@
         <v>36440</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="163" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A163" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4754,7 +4811,7 @@
         <v>36465</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="164" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A164" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4780,7 +4837,7 @@
         <v>36475</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="165" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A165" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4806,7 +4863,7 @@
         <v>36540</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="166" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A166" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4832,7 +4889,7 @@
         <v>36565</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="167" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A167" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4858,7 +4915,7 @@
         <v>36555</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="168" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A168" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4884,7 +4941,7 @@
         <v>36540</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="169" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A169" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4910,7 +4967,7 @@
         <v>36605</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="170" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A170" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4936,7 +4993,7 @@
         <v>36605</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="171" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A171" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4962,7 +5019,7 @@
         <v>36680</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="172" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A172" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4988,7 +5045,7 @@
         <v>36660</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="173" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A173" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5014,7 +5071,7 @@
         <v>36705</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="174" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A174" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5040,7 +5097,7 @@
         <v>36745</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="175" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A175" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5066,7 +5123,7 @@
         <v>36730</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="176" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A176" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5092,7 +5149,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="177" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A177" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5118,7 +5175,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="178" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A178" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5144,7 +5201,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="179" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A179" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5170,7 +5227,7 @@
         <v>36780</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="180" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A180" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5196,7 +5253,7 @@
         <v>36875</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="181" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A181" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5222,7 +5279,7 @@
         <v>36885</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="182" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A182" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5248,7 +5305,7 @@
         <v>36885</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="183" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A183" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5274,7 +5331,7 @@
         <v>36890</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="184" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A184" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5300,7 +5357,7 @@
         <v>36875</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="185" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A185" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5326,7 +5383,7 @@
         <v>36900</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="186" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A186" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5352,7 +5409,7 @@
         <v>36905</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="187" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A187" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5378,7 +5435,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="188" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A188" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5404,7 +5461,7 @@
         <v>36990</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="189" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A189" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5430,7 +5487,7 @@
         <v>37015</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="190" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A190" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5456,7 +5513,7 @@
         <v>37010</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="191" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A191" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5482,7 +5539,7 @@
         <v>37020</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="192" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A192" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5508,7 +5565,7 @@
         <v>37060</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="193" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A193" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5534,7 +5591,7 @@
         <v>37040</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="194" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A194" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5560,7 +5617,7 @@
         <v>37060</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="195" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A195" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5586,7 +5643,7 @@
         <v>37085</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="196" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A196" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5612,7 +5669,7 @@
         <v>37130</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="197" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A197" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5638,7 +5695,7 @@
         <v>37125</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="198" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A198" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5664,7 +5721,7 @@
         <v>37125</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="199" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A199" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5690,7 +5747,7 @@
         <v>37135</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="200" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A200" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5716,7 +5773,7 @@
         <v>37185</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="201" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A201" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5742,7 +5799,7 @@
         <v>37165</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="202" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A202" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5768,7 +5825,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="203" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A203" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5794,7 +5851,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="204" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A204" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5820,7 +5877,7 @@
         <v>37270</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="205" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A205" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5846,7 +5903,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="206" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A206" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5872,7 +5929,7 @@
         <v>37740</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="207" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A207" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5898,7 +5955,7 @@
         <v>37750</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="208" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A208" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5924,7 +5981,7 @@
         <v>37740</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="209" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A209" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5950,7 +6007,7 @@
         <v>37755</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="210" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A210" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5976,7 +6033,7 @@
         <v>37755</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="211" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A211" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6002,7 +6059,7 @@
         <v>37800</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="212" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A212" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6028,7 +6085,7 @@
         <v>37835</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="213" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A213" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6054,7 +6111,7 @@
         <v>37860</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="214" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A214" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6080,7 +6137,7 @@
         <v>37880</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="215" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A215" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6106,7 +6163,7 @@
         <v>37905</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="216" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A216" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6132,7 +6189,7 @@
         <v>37915</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="217" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A217" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6158,7 +6215,7 @@
         <v>37980</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="218" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A218" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6184,7 +6241,7 @@
         <v>38005</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="219" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A219" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6210,7 +6267,7 @@
         <v>37995</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="220" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A220" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6236,7 +6293,7 @@
         <v>37980</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="221" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A221" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6262,7 +6319,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="222" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A222" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6288,7 +6345,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="223" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A223" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6314,7 +6371,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="224" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A224" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6340,7 +6397,7 @@
         <v>38120</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="225" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A225" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6366,7 +6423,7 @@
         <v>38145</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="226" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A226" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6392,7 +6449,7 @@
         <v>38100</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="227" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A227" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6418,7 +6475,7 @@
         <v>38145</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="228" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A228" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6444,7 +6501,7 @@
         <v>38185</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="229" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A229" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6470,7 +6527,7 @@
         <v>38170</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="230" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A230" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6496,7 +6553,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="231" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A231" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6522,7 +6579,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="232" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A232" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6548,7 +6605,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="233" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A233" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6574,7 +6631,7 @@
         <v>38220</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="234" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A234" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6600,7 +6657,7 @@
         <v>38315</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="235" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A235" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6626,7 +6683,7 @@
         <v>38325</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="236" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A236" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6652,7 +6709,7 @@
         <v>38325</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="237" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A237" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6678,7 +6735,7 @@
         <v>38330</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="238" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A238" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6704,7 +6761,7 @@
         <v>38315</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="239" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A239" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6730,7 +6787,7 @@
         <v>38340</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="240" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A240" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6756,7 +6813,7 @@
         <v>38345</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="241" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A241" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6782,7 +6839,7 @@
         <v>38440</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="242" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A242" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6808,7 +6865,7 @@
         <v>38430</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="243" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A243" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6834,7 +6891,7 @@
         <v>38455</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="244" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A244" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6860,7 +6917,7 @@
         <v>38450</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="245" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A245" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6886,7 +6943,7 @@
         <v>38460</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="246" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A246" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6912,7 +6969,7 @@
         <v>38500</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="247" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A247" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6938,7 +6995,7 @@
         <v>38480</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="248" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A248" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6964,7 +7021,7 @@
         <v>38500</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="249" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A249" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6990,7 +7047,7 @@
         <v>38525</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="250" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A250" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7016,7 +7073,7 @@
         <v>38570</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="251" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A251" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7042,7 +7099,7 @@
         <v>38565</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="252" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A252" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7068,7 +7125,7 @@
         <v>38565</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="253" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A253" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7094,7 +7151,7 @@
         <v>38575</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="254" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A254" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7120,7 +7177,7 @@
         <v>38625</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="255" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A255" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7146,7 +7203,7 @@
         <v>38605</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="256" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A256" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7172,7 +7229,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="257" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A257" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7198,7 +7255,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="258" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A258" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7224,7 +7281,7 @@
         <v>38710</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="259" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A259" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7250,7 +7307,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="260" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A260" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7276,7 +7333,7 @@
         <v>39180</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="261" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A261" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7302,7 +7359,7 @@
         <v>39195</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="262" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A262" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7328,7 +7385,7 @@
         <v>39195</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="263" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A263" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7354,7 +7411,7 @@
         <v>39190</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="264" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A264" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7380,7 +7437,7 @@
         <v>39180</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="265" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A265" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7406,7 +7463,7 @@
         <v>39275</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="266" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A266" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7432,7 +7489,7 @@
         <v>39320</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="267" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A267" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7458,7 +7515,7 @@
         <v>39355</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="268" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A268" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7484,7 +7541,7 @@
         <v>39420</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="269" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A269" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7510,7 +7567,7 @@
         <v>39445</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="270" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A270" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7536,7 +7593,7 @@
         <v>39490</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="271" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A271" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7562,7 +7619,7 @@
         <v>39435</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="272" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A272" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7588,7 +7645,7 @@
         <v>39420</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="273" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A273" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7614,7 +7671,7 @@
         <v>39485</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="274" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A274" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7640,7 +7697,7 @@
         <v>39560</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="275" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A275" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7666,7 +7723,7 @@
         <v>39540</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="276" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A276" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7692,7 +7749,7 @@
         <v>39585</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="277" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A277" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7718,7 +7775,7 @@
         <v>39625</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="278" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A278" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7744,7 +7801,7 @@
         <v>39630</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="279" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A279" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7770,7 +7827,7 @@
         <v>39710</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="280" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A280" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7796,7 +7853,7 @@
         <v>39650</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="281" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A281" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7822,7 +7879,7 @@
         <v>39650</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="282" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A282" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7848,7 +7905,7 @@
         <v>39660</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="283" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A283" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7874,7 +7931,7 @@
         <v>39755</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="284" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A284" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7900,7 +7957,7 @@
         <v>39745</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="285" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A285" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7926,7 +7983,7 @@
         <v>39765</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="286" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A286" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7952,7 +8009,7 @@
         <v>39770</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="287" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A287" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7978,7 +8035,7 @@
         <v>39755</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="288" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A288" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8004,7 +8061,7 @@
         <v>39780</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="289" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A289" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8030,7 +8087,7 @@
         <v>39880</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="290" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A290" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8056,7 +8113,7 @@
         <v>39870</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="291" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A291" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8082,7 +8139,7 @@
         <v>39895</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="292" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A292" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8108,7 +8165,7 @@
         <v>39900</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="293" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A293" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8134,7 +8191,7 @@
         <v>39940</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="294" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A294" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8160,7 +8217,7 @@
         <v>39920</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="295" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A295" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8186,7 +8243,7 @@
         <v>39965</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="296" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A296" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8212,7 +8269,7 @@
         <v>40010</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="297" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A297" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8238,7 +8295,7 @@
         <v>40005</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="298" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A298" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8264,7 +8321,7 @@
         <v>40015</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="299" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A299" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8290,7 +8347,7 @@
         <v>40065</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="300" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A300" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8316,7 +8373,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="301" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A301" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8342,7 +8399,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="302" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A302" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8368,7 +8425,7 @@
         <v>40150</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="303" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A303" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8394,7 +8451,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="304" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A304" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8420,7 +8477,7 @@
         <v>40620</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="305" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A305" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8446,7 +8503,7 @@
         <v>40630</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="306" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A306" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8472,7 +8529,7 @@
         <v>40620</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="307" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A307" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8498,7 +8555,7 @@
         <v>40635</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="308" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A308" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8524,7 +8581,7 @@
         <v>40635</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="309" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A309" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8550,7 +8607,7 @@
         <v>40715</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="310" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A310" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8576,7 +8633,7 @@
         <v>40760</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="311" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A311" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8602,7 +8659,7 @@
         <v>40785</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="312" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A312" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8628,7 +8685,7 @@
         <v>40795</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="313" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A313" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8654,7 +8711,7 @@
         <v>40860</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="314" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A314" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8680,7 +8737,7 @@
         <v>40885</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="315" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A315" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8706,7 +8763,7 @@
         <v>40875</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="316" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A316" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8732,7 +8789,7 @@
         <v>40860</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="317" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A317" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8758,7 +8815,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="318" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A318" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8784,7 +8841,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="319" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A319" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8810,7 +8867,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="320" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A320" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8836,7 +8893,7 @@
         <v>41000</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="321" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A321" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8862,7 +8919,7 @@
         <v>40980</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="322" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A322" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8888,7 +8945,7 @@
         <v>41025</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="323" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A323" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8914,7 +8971,7 @@
         <v>41025</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="324" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A324" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8940,7 +8997,7 @@
         <v>41065</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="325" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A325" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8966,7 +9023,7 @@
         <v>41050</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="326" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A326" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8992,7 +9049,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="327" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A327" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9018,7 +9075,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="328" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A328" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9044,7 +9101,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="329" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A329" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9070,7 +9127,7 @@
         <v>41100</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="330" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A330" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9096,7 +9153,7 @@
         <v>41195</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="331" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A331" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9122,7 +9179,7 @@
         <v>41205</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="332" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A332" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9148,7 +9205,7 @@
         <v>41205</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="333" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A333" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9174,7 +9231,7 @@
         <v>41210</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="334" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A334" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9200,7 +9257,7 @@
         <v>41195</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="335" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A335" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9226,7 +9283,7 @@
         <v>41220</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="336" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A336" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9252,7 +9309,7 @@
         <v>41225</v>
       </c>
     </row>
-    <row r="337" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="337" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A337" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9278,7 +9335,7 @@
         <v>41320</v>
       </c>
     </row>
-    <row r="338" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="338" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A338" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9304,7 +9361,7 @@
         <v>41310</v>
       </c>
     </row>
-    <row r="339" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="339" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A339" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9330,7 +9387,7 @@
         <v>41335</v>
       </c>
     </row>
-    <row r="340" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="340" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A340" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9356,7 +9413,7 @@
         <v>41330</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="341" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A341" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9382,7 +9439,7 @@
         <v>41340</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="342" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A342" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9408,7 +9465,7 @@
         <v>41380</v>
       </c>
     </row>
-    <row r="343" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="343" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A343" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9434,7 +9491,7 @@
         <v>41360</v>
       </c>
     </row>
-    <row r="344" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="344" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A344" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9460,7 +9517,7 @@
         <v>41380</v>
       </c>
     </row>
-    <row r="345" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="345" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A345" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9486,7 +9543,7 @@
         <v>41405</v>
       </c>
     </row>
-    <row r="346" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="346" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A346" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9512,7 +9569,7 @@
         <v>41450</v>
       </c>
     </row>
-    <row r="347" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="347" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A347" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9538,7 +9595,7 @@
         <v>41445</v>
       </c>
     </row>
-    <row r="348" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="348" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A348" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9564,7 +9621,7 @@
         <v>41445</v>
       </c>
     </row>
-    <row r="349" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="349" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A349" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9590,7 +9647,7 @@
         <v>41455</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="350" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A350" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9616,7 +9673,7 @@
         <v>41505</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="351" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A351" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9642,7 +9699,7 @@
         <v>41485</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="352" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A352" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9668,7 +9725,7 @@
         <v>41575</v>
       </c>
     </row>
-    <row r="353" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="353" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A353" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9694,7 +9751,7 @@
         <v>41575</v>
       </c>
     </row>
-    <row r="354" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="354" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A354" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9720,7 +9777,7 @@
         <v>41590</v>
       </c>
     </row>
-    <row r="355" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="355" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A355" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9765,7 +9822,7 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:10" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:10" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -9797,7 +9854,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:10" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2">
         <v>35</v>
       </c>
@@ -9848,7 +9905,7 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s" s="1">
         <v>36</v>
       </c>
@@ -9874,7 +9931,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2" t="s" s="1">
         <v>24</v>
       </c>
@@ -9900,7 +9957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="3" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A3" t="s" s="1">
         <v>9</v>
       </c>
@@ -9926,7 +9983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="4" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A4" t="s" s="1">
         <v>16</v>
       </c>
@@ -9952,7 +10009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="5" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A5" t="s" s="1">
         <v>25</v>
       </c>
@@ -9978,7 +10035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="6" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A6" t="s" s="1">
         <v>22</v>
       </c>
@@ -10004,7 +10061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="7" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A7" t="s" s="1">
         <v>17</v>
       </c>
@@ -10030,7 +10087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="8" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A8" t="s" s="1">
         <v>10</v>
       </c>
@@ -10056,7 +10113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="9" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A9" t="s" s="1">
         <v>20</v>
       </c>
@@ -10082,7 +10139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="10" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A10" t="s" s="1">
         <v>11</v>
       </c>
@@ -10108,7 +10165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="11" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A11" t="s" s="1">
         <v>29</v>
       </c>
@@ -10134,7 +10191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="12" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A12" t="s" s="1">
         <v>23</v>
       </c>
@@ -10160,7 +10217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="13" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A13" t="s" s="1">
         <v>14</v>
       </c>
@@ -10186,7 +10243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="14" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A14" t="s" s="1">
         <v>27</v>
       </c>
@@ -10212,7 +10269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="15" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A15" t="s" s="1">
         <v>13</v>
       </c>
@@ -10238,7 +10295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="16" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A16" t="s" s="1">
         <v>44</v>
       </c>
@@ -10264,7 +10321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="17" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A17" t="s" s="1">
         <v>28</v>
       </c>
@@ -10290,7 +10347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="18" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A18" t="s" s="1">
         <v>8</v>
       </c>
@@ -10316,7 +10373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="19" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A19" t="s" s="1">
         <v>26</v>
       </c>
@@ -10342,7 +10399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="20" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A20" t="s" s="1">
         <v>15</v>
       </c>
@@ -10368,7 +10425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="21" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A21" t="s" s="1">
         <v>18</v>
       </c>
@@ -10394,7 +10451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="22" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A22" t="s" s="1">
         <v>21</v>
       </c>
@@ -10420,7 +10477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="false" customFormat="false" ht="12.8" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="23" spans="1:8" hidden="false" outlineLevel="0" ht="12.8" customHeight="false" collapsed="false" customFormat="false">
       <c r="A23" t="s" s="0">
         <v>12</v>
       </c>
@@ -10465,156 +10522,156 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A1" t="s" s="1">
-        <v>45</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>46</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>47</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>48</v>
-      </c>
-      <c r="E1" t="s" s="1">
+    <row r="1" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2">
+        <v>5895</v>
+      </c>
+      <c r="D2">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A2" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C2" t="n" s="3">
-        <v>5895</v>
-      </c>
-      <c r="D2" t="n" s="4">
-        <v>49</v>
-      </c>
-      <c r="E2" t="n" s="4">
+      <c r="E2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A3" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s" s="3">
-        <v>11</v>
-      </c>
-      <c r="C3" t="n" s="3">
+    <row r="3" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n" s="1">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3" t="n" s="1">
+    </row>
+    <row r="4" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A4" t="s" s="1">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C4" t="n" s="3">
+    <row r="5" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5">
         <v>0</v>
       </c>
-      <c r="D4" t="n" s="1">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="E4" t="n" s="1">
+    </row>
+    <row r="6" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A5" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="B5" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="C5" t="n" s="3">
+    <row r="7" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="D5" t="n" s="1">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="E5" t="n" s="1">
+    </row>
+    <row r="8" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A6" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="B6" t="s" s="3">
-        <v>10</v>
-      </c>
-      <c r="C6" t="n" s="3">
+    <row r="9" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9">
         <v>0</v>
       </c>
-      <c r="D6" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A7" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="B7" t="s" s="3">
-        <v>12</v>
-      </c>
-      <c r="C7" t="n" s="3">
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="D7" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A8" t="s" s="1">
-        <v>56</v>
-      </c>
-      <c r="B8" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C8" t="n" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A9" t="s" s="1">
-        <v>57</v>
-      </c>
-      <c r="B9" t="s" s="3">
-        <v>13</v>
-      </c>
-      <c r="C9" t="n" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n" s="1">
+      <c r="E9">
         <v>1</v>
       </c>
     </row>

--- a/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_7.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_7.xlsx
@@ -9848,10 +9848,10 @@
         <v>480</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>78.0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12.0</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -9916,19 +9916,19 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -9951,7 +9951,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -9968,16 +9968,16 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -9994,19 +9994,19 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -10017,19 +10017,19 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -10073,10 +10073,10 @@
         <v>5895</v>
       </c>
       <c r="D2">
-        <v>49</v>
+        <v>77.0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
